--- a/Book6.xlsx
+++ b/Book6.xlsx
@@ -5,15 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuandong.xu\Desktop\日本語\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jpword\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B706208-72B9-44ED-B61D-C6FFBFA71397}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E095F38-0F99-47FF-94A7-A98311979D07}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12075" xr2:uid="{8A6F6009-7A9D-41EF-B92B-219E99C30600}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12075" activeTab="2" xr2:uid="{8A6F6009-7A9D-41EF-B92B-219E99C30600}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="784">
   <si>
     <t>第一章｜原因・理由（15条）</t>
   </si>
@@ -1495,6 +1497,1223 @@
   </si>
   <si>
     <t>「わりに」表示从某个标准来看，结果出乎意料或不成比例，常用于客观陈述反差</t>
+  </si>
+  <si>
+    <t>文法</t>
+  </si>
+  <si>
+    <t>接続</t>
+  </si>
+  <si>
+    <t>意味</t>
+  </si>
+  <si>
+    <t>〜ものの</t>
+  </si>
+  <si>
+    <t>動/い形/な形/名の名詞修飾形 + ものの</t>
+  </si>
+  <si>
+    <t>虽然…但是…</t>
+  </si>
+  <si>
+    <t>〜にもかかわらず</t>
+  </si>
+  <si>
+    <t>動/い形/な形/名の名詞修飾形 + にもかかわらず</t>
+  </si>
+  <si>
+    <t>尽管…却…</t>
+  </si>
+  <si>
+    <t>〜（よ）うにも〜ない</t>
+  </si>
+  <si>
+    <t>即使想…也不能…</t>
+  </si>
+  <si>
+    <t>〜つつ（も）</t>
+  </si>
+  <si>
+    <t>〜さえ〜ば</t>
+  </si>
+  <si>
+    <t>只要…就…</t>
+  </si>
+  <si>
+    <t>〜たところで</t>
+  </si>
+  <si>
+    <t>即使…也（白费）…</t>
+  </si>
+  <si>
+    <t>〜（よ）うものなら</t>
+  </si>
+  <si>
+    <t>如果…可就会…</t>
+  </si>
+  <si>
+    <t>〜以上（は）</t>
+  </si>
+  <si>
+    <t>動/い形/な形/名の名詞修飾形 + 以上（は）</t>
+  </si>
+  <si>
+    <t>既然…就…</t>
+  </si>
+  <si>
+    <t>〜限り（は）</t>
+  </si>
+  <si>
+    <t>〜に関して（は/も）</t>
+  </si>
+  <si>
+    <t>关于…</t>
+  </si>
+  <si>
+    <t>〜に対して（は/も）</t>
+  </si>
+  <si>
+    <t>对…；与…相反</t>
+  </si>
+  <si>
+    <t>〜に伴って</t>
+  </si>
+  <si>
+    <t>随着…</t>
+  </si>
+  <si>
+    <t>〜につれて</t>
+  </si>
+  <si>
+    <t>〜に基づいて</t>
+  </si>
+  <si>
+    <t>基于…/按照…</t>
+  </si>
+  <si>
+    <t>〜に応えて</t>
+  </si>
+  <si>
+    <t>响应…/应…</t>
+  </si>
+  <si>
+    <t>〜ばかりに</t>
+  </si>
+  <si>
+    <t>動/い形/な形/名の名詞修飾形 + ばかりに</t>
+  </si>
+  <si>
+    <t>〜ものだから</t>
+  </si>
+  <si>
+    <t>動/い形/な形/名の名詞修飾形 + ものだから</t>
+  </si>
+  <si>
+    <t>因为…（辩解）</t>
+  </si>
+  <si>
+    <t>〜おかげで</t>
+  </si>
+  <si>
+    <t>動/い形/な形/名の名詞修飾形 + おかげで</t>
+  </si>
+  <si>
+    <t>〜せいで</t>
+  </si>
+  <si>
+    <t>動/い形/な形/名の名詞修飾形 + せいで</t>
+  </si>
+  <si>
+    <t>〜からいうと/からいえば</t>
+  </si>
+  <si>
+    <t>从…来说</t>
+  </si>
+  <si>
+    <t>〜から見ると/から見れば</t>
+  </si>
+  <si>
+    <t>从…来看</t>
+  </si>
+  <si>
+    <t>〜として（は）</t>
+  </si>
+  <si>
+    <t>作为…</t>
+  </si>
+  <si>
+    <t>〜かねる</t>
+  </si>
+  <si>
+    <t>难以…/不能…</t>
+  </si>
+  <si>
+    <t>〜がたい</t>
+  </si>
+  <si>
+    <t>难以…</t>
+  </si>
+  <si>
+    <t>〜きれない</t>
+  </si>
+  <si>
+    <t>不能完全…/…不完</t>
+  </si>
+  <si>
+    <t>〜たまま</t>
+  </si>
+  <si>
+    <t>〜つつ（ある）</t>
+  </si>
+  <si>
+    <t>正在…</t>
+  </si>
+  <si>
+    <t>〜わけではない</t>
+  </si>
+  <si>
+    <t>動/い形/な形/名の名詞修飾形 + わけではない</t>
+  </si>
+  <si>
+    <t>并不是…</t>
+  </si>
+  <si>
+    <t>〜ことになっている</t>
+  </si>
+  <si>
+    <t>按规定…/预定…</t>
+  </si>
+  <si>
+    <t>テストポイント（考点）</t>
+  </si>
+  <si>
+    <t>「〜けど」的书面语。 后项接事实，不接意志表现（如〜たい/つもり）。</t>
+  </si>
+  <si>
+    <t>動ます/い形/名 + ながら（も）</t>
+  </si>
+  <si>
+    <t>比「〜のに」生硬。 多接状态动词（ある/いる）或可能形。</t>
+  </si>
+  <si>
+    <t>最正式的「〜のに」。 考点常为与「〜のに」的区分使用，非常正式。</t>
+  </si>
+  <si>
+    <t>意向形 + にも + 可能形の否定</t>
+  </si>
+  <si>
+    <t>表示“物理/能力上不可能”。 特征为同一动词重复（如：起きようにも起きられない）。</t>
+  </si>
+  <si>
+    <t>動ます + つつ（も）</t>
+  </si>
+  <si>
+    <t>与「〜ながら（も）」几乎相同。 书面语。注意与「〜つつある」（进行中）的区别。</t>
+  </si>
+  <si>
+    <t>動ます/い形~~く~~/名 + さえ + 〜ば</t>
+  </si>
+  <si>
+    <t>“只要这一条件就够了”。 常考语序：名词＋「さえ＋动词ば形」。</t>
+  </si>
+  <si>
+    <t>動た形 + ところで</t>
+  </si>
+  <si>
+    <t>表示“徒劳/期待落空”。 后项多接否定或消极意义词语。</t>
+  </si>
+  <si>
+    <t>意向形 + ものなら</t>
+  </si>
+  <si>
+    <t>表示“会酿成大祸”的警告。 假设未发生的事，后项为坏结果。</t>
+  </si>
+  <si>
+    <t>表示“强烈的责任/决心”。 后项接说话人的意志、义务、推测（如〜なければならない/〜はずだ）。</t>
+  </si>
+  <si>
+    <t>動辞書形/ない形 + 限り（は）</t>
+  </si>
+  <si>
+    <t>“只要该状态持续”。 后项也持续。否定形「〜ない限り」也是高频考点。</t>
+  </si>
+  <si>
+    <t>名 + に関して</t>
+  </si>
+  <si>
+    <t>「〜について」的正式说法。 用于商务文书或正式场合。</t>
+  </si>
+  <si>
+    <t>名 + に対して</t>
+  </si>
+  <si>
+    <t>两个意思： ①对象（感情/行为指向）；②对比（与…相反）。对比用法常考。</t>
+  </si>
+  <si>
+    <t>名/動辞書形 + に伴って</t>
+  </si>
+  <si>
+    <t>表示“同时发生的变化”。 伴随增减、变化。比「〜につれて」正式。</t>
+  </si>
+  <si>
+    <t>動辞書形/名 + につれて</t>
+  </si>
+  <si>
+    <t>“一方变化，另一方也变化”。 常与「〜に従って」「〜とともに」替换出题。</t>
+  </si>
+  <si>
+    <t>名 + に基づいて</t>
+  </si>
+  <si>
+    <t>表示“基础/依据”。 用于事实、数据、经验、规则等确凿依据。</t>
+  </si>
+  <si>
+    <t>名 + に応えて</t>
+  </si>
+  <si>
+    <t>表示“回应期待/要求”。 应对方要求采取行动。</t>
+  </si>
+  <si>
+    <t>就是因为…</t>
+  </si>
+  <si>
+    <t>表示“仅因这一个原因导致坏结果”。 带有懊悔、遗憾的情绪。</t>
+  </si>
+  <si>
+    <t>用于辩解。 为自己的行为正当化，或用于意料之外的结果时。</t>
+  </si>
+  <si>
+    <t>多亏了…</t>
+  </si>
+  <si>
+    <t>“感谢带来好结果”。 但也可反讽用于坏结果，需根据上下文判断。</t>
+  </si>
+  <si>
+    <t>都怪…</t>
+  </si>
+  <si>
+    <t>表示“坏结果的原因”。 带有推卸责任、不满的语气。</t>
+  </si>
+  <si>
+    <t>名 + からいうと</t>
+  </si>
+  <si>
+    <t>“从该立场/观点判断”。 与「〜から見ると」区分：言う→意见/评价，見る→外观/观察。</t>
+  </si>
+  <si>
+    <t>名 + から見ると</t>
+  </si>
+  <si>
+    <t>表示“从外观/外部观察”。 基于外表或状况的判断。</t>
+  </si>
+  <si>
+    <t>名 + として</t>
+  </si>
+  <si>
+    <t>明确立场、资格、种类。 常与「〜にしては」（作为…却意外）混淆，注意区分。</t>
+  </si>
+  <si>
+    <t>動ます + かねる</t>
+  </si>
+  <si>
+    <t>表示“心理上难以做到”，是委婉拒绝的表达。 商务邮件中「いたしかねます」高频。</t>
+  </si>
+  <si>
+    <t>動ます + がたい</t>
+  </si>
+  <si>
+    <t>表示“客观上很难做到”。 如「耐え難い」（难以忍受）等。</t>
+  </si>
+  <si>
+    <t>動ます + きれない</t>
+  </si>
+  <si>
+    <t>表示“数量/程度太多而无法完成”。 典型例子：「食べきれない」「数えきれない」。</t>
+  </si>
+  <si>
+    <t>動た形 + まま</t>
+  </si>
+  <si>
+    <t>保持着…状态</t>
+  </si>
+  <si>
+    <t>表示状态未改变。 常带有“本该改变却未变”的违和感。</t>
+  </si>
+  <si>
+    <t>動ます + つつある</t>
+  </si>
+  <si>
+    <t>表示“变化的过程中”。 与「〜ている」不同，强调逐渐变化中。</t>
+  </si>
+  <si>
+    <t>表示部分否定。 不要误解为全部否定。如「みんなが〜わけではない」＝并非所有人都…</t>
+  </si>
+  <si>
+    <t>動辞書形/ない形 + ことになっている</t>
+  </si>
+  <si>
+    <t>表示“客观规则/决定”。 不用于自己决定的事情（自己决定用「〜ことにしている」）。</t>
+  </si>
+  <si>
+    <t>試験で特に注意すべき「三大トラップ」（三大考点陷阱）</t>
+  </si>
+  <si>
+    <t>上記の表を踏まえ、試験で特に気をつけるべきポイントをまとめます。</t>
+  </si>
+  <si>
+    <t>1. 接続のトラップ（接续陷阱）</t>
+  </si>
+  <si>
+    <t>例：「〜に基づいて」前面必须是「名词」（不能接动词）</t>
+  </si>
+  <si>
+    <t>例：「〜がたい」前面是「动词ます形」（不是「动词た形」）</t>
+  </si>
+  <si>
+    <t>2. 多義語のトラップ（一词多义陷阱）</t>
+  </si>
+  <si>
+    <t>「〜つつ」 → ①逆接（〜ながらも） ②進行（〜つつある）</t>
+  </si>
+  <si>
+    <t>「〜ながら」 → ①同時進行（音楽を聞きながら） ②逆接（悪いと知りながら）</t>
+  </si>
+  <si>
+    <t>3. 意味の限定トラップ（语义限定陷阱）</t>
+  </si>
+  <si>
+    <t>「〜ばかりに」 → 必须是坏结果</t>
+  </si>
+  <si>
+    <t>「〜おかげで」 → 基本是好结果（如果是坏结果则是反讽）</t>
+  </si>
+  <si>
+    <t>「〜ものだから」 → 用于说话人自己的情况/辩解（不能用于他人）</t>
+  </si>
+  <si>
+    <t>〜ものの</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>【「もの」シリーズ完全比較表】</t>
+  </si>
+  <si>
+    <t>後件の特徴</t>
+  </si>
+  <si>
+    <t>名詞修飾形 + ものの</t>
+  </si>
+  <si>
+    <t>事実が来る</t>
+  </si>
+  <si>
+    <t>因为…（所以）…</t>
+  </si>
+  <si>
+    <t>名詞修飾形 + ものだから</t>
+  </si>
+  <si>
+    <t>結果/説明</t>
+  </si>
+  <si>
+    <t>〜もので</t>
+  </si>
+  <si>
+    <t>名詞修飾形 + もので</t>
+  </si>
+  <si>
+    <t>結果/説明（やや丁寧）</t>
+  </si>
+  <si>
+    <t>〜ものなら</t>
+  </si>
+  <si>
+    <t>如果…的话…</t>
+  </si>
+  <si>
+    <t>大変なことになる</t>
+  </si>
+  <si>
+    <t>〜ながら（も）</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>🧠 一句话核心区别</t>
+  </si>
+  <si>
+    <t>核心感觉</t>
+  </si>
+  <si>
+    <t>ものの</t>
+  </si>
+  <si>
+    <t>虽然…但（单纯落差）</t>
+  </si>
+  <si>
+    <t>とはいえ</t>
+  </si>
+  <si>
+    <t>虽说…可是（让步感）</t>
+  </si>
+  <si>
+    <t>ながら（も）</t>
+  </si>
+  <si>
+    <t>明知…却（心理矛盾）</t>
+  </si>
+  <si>
+    <t>くせに</t>
+  </si>
+  <si>
+    <t>明明…却（批评不满）</t>
+  </si>
+  <si>
+    <t>にもかかわらず</t>
+  </si>
+  <si>
+    <t>尽管…仍然（客观正式）</t>
+  </si>
+  <si>
+    <t>どころか</t>
+  </si>
+  <si>
+    <t>别说…反而（程度反转）</t>
+  </si>
+  <si>
+    <t>ばかりか</t>
+  </si>
+  <si>
+    <t>不仅…而且（正向追加）</t>
+  </si>
+  <si>
+    <t>① 〜ものの</t>
+  </si>
+  <si>
+    <t>🔹 特点</t>
+  </si>
+  <si>
+    <t>书面语</t>
+  </si>
+  <si>
+    <t>单纯“预期落差”</t>
+  </si>
+  <si>
+    <t>后项多为不理想结果</t>
+  </si>
+  <si>
+    <t>🔹 例</t>
+  </si>
+  <si>
+    <t>日本に10年住んでいるものの、敬語は苦手だ。</t>
+  </si>
+  <si>
+    <t>👉 住10年 → 按理说会好</t>
+  </si>
+  <si>
+    <t>👉 现实 → 不好</t>
+  </si>
+  <si>
+    <t>② 〜とはいえ</t>
+  </si>
+  <si>
+    <t>虽说…不过…</t>
+  </si>
+  <si>
+    <t>比 ものの 更“让步”</t>
+  </si>
+  <si>
+    <t>带“承认对方观点”的感觉</t>
+  </si>
+  <si>
+    <t>子供とはいえ、責任はある。</t>
+  </si>
+  <si>
+    <t>👉 承认是孩子</t>
+  </si>
+  <si>
+    <t>👉 但仍然有责任</t>
+  </si>
+  <si>
+    <t>📌 常用于议论文</t>
+  </si>
+  <si>
+    <t>③ 〜ながら（も）</t>
+  </si>
+  <si>
+    <t>明明…却…</t>
+  </si>
+  <si>
+    <t>多用于“心理矛盾”</t>
+  </si>
+  <si>
+    <t>主语通常一致</t>
+  </si>
+  <si>
+    <t>危険だと知りながら、挑戦した。</t>
+  </si>
+  <si>
+    <t>👉 知道危险</t>
+  </si>
+  <si>
+    <t>👉 却去做</t>
+  </si>
+  <si>
+    <t>⚠ 常考点：主语必须一致</t>
+  </si>
+  <si>
+    <t>④ 〜くせに</t>
+  </si>
+  <si>
+    <t>明明…却…（带批评）</t>
+  </si>
+  <si>
+    <t>强烈不满</t>
+  </si>
+  <si>
+    <t>多口语</t>
+  </si>
+  <si>
+    <t>带感情色彩</t>
+  </si>
+  <si>
+    <t>何も知らないくせに、偉そうに言う。</t>
+  </si>
+  <si>
+    <t>👉 情绪明显</t>
+  </si>
+  <si>
+    <t>⚠ 不能用于上级、正式场合</t>
+  </si>
+  <si>
+    <t>⑤ 〜にもかかわらず</t>
+  </si>
+  <si>
+    <t>尽管…仍然…</t>
+  </si>
+  <si>
+    <t>最正式</t>
+  </si>
+  <si>
+    <t>客观陈述</t>
+  </si>
+  <si>
+    <t>常见于新闻、论文</t>
+  </si>
+  <si>
+    <t>雨にもかかわらず、試合は行われた。</t>
+  </si>
+  <si>
+    <t>👉 非常正式表达</t>
+  </si>
+  <si>
+    <t>⑥ 〜どころか</t>
+  </si>
+  <si>
+    <t>别说…反而…</t>
+  </si>
+  <si>
+    <t>程度反转</t>
+  </si>
+  <si>
+    <t>常和否定预期连用</t>
+  </si>
+  <si>
+    <t>良くなるどころか、悪化した。</t>
+  </si>
+  <si>
+    <t>👉 本来期待变好</t>
+  </si>
+  <si>
+    <t>👉 实际更糟</t>
+  </si>
+  <si>
+    <t>⑦ 〜ばかりか</t>
+  </si>
+  <si>
+    <t>不仅…而且…</t>
+  </si>
+  <si>
+    <t>正向追加</t>
+  </si>
+  <si>
+    <t>稍正式</t>
+  </si>
+  <si>
+    <t>常用于强调</t>
+  </si>
+  <si>
+    <t>彼は英語ばかりか、中国語も話せる。</t>
+  </si>
+  <si>
+    <t>👉 不止一个</t>
+  </si>
+  <si>
+    <t>🎯 情绪强度排序（考试重要）</t>
+  </si>
+  <si>
+    <t>弱 → 强</t>
+  </si>
+  <si>
+    <t>ながらも</t>
+  </si>
+  <si>
+    <t>くせに（最强情绪）</t>
+  </si>
+  <si>
+    <t>🧨 N2考试最常混淆点</t>
+  </si>
+  <si>
+    <t>① ものの vs とはいえ</t>
+  </si>
+  <si>
+    <t>结果不理想</t>
+  </si>
+  <si>
+    <t>承认事实再转折</t>
+  </si>
+  <si>
+    <t>叙述型</t>
+  </si>
+  <si>
+    <t>议论型</t>
+  </si>
+  <si>
+    <t>② ながら vs くせに</t>
+  </si>
+  <si>
+    <t>ながら</t>
+  </si>
+  <si>
+    <t>自己行为</t>
+  </si>
+  <si>
+    <t>批评别人</t>
+  </si>
+  <si>
+    <t>无强烈情绪</t>
+  </si>
+  <si>
+    <t>有不满</t>
+  </si>
+  <si>
+    <t>③ どころか vs ばかりか</t>
+  </si>
+  <si>
+    <t>反向升级</t>
+  </si>
+  <si>
+    <t>变差</t>
+  </si>
+  <si>
+    <t>变强</t>
+  </si>
+  <si>
+    <t>🧠 秒杀判断技巧</t>
+  </si>
+  <si>
+    <t>看到句子问自己：</t>
+  </si>
+  <si>
+    <t>1️⃣ 有没有情绪？</t>
+  </si>
+  <si>
+    <t>→ 有批评 → くせに</t>
+  </si>
+  <si>
+    <t>2️⃣ 是客观新闻？</t>
+  </si>
+  <si>
+    <t>→ にもかかわらず</t>
+  </si>
+  <si>
+    <t>3️⃣ 是心理矛盾？</t>
+  </si>
+  <si>
+    <t>→ ながら</t>
+  </si>
+  <si>
+    <t>4️⃣ 是“反而更糟”？</t>
+  </si>
+  <si>
+    <t>→ どころか</t>
+  </si>
+  <si>
+    <t>5️⃣ 是“不仅而且”？</t>
+  </si>
+  <si>
+    <t>→ ばかりか</t>
+  </si>
+  <si>
+    <t>6️⃣ 只是普通落差？</t>
+  </si>
+  <si>
+    <t>→ ものの</t>
+  </si>
+  <si>
+    <t>7️⃣ 是让步议论？</t>
+  </si>
+  <si>
+    <t>→ とはいえ</t>
+  </si>
+  <si>
+    <t>🧠 第一步：先判断“结构类型”</t>
+  </si>
+  <si>
+    <t>看到一句逆接，先问自己：</t>
+  </si>
+  <si>
+    <t>① 是“单纯落差”？</t>
+  </si>
+  <si>
+    <t>预期 A → 应该 B</t>
+  </si>
+  <si>
+    <t>实际 A → 却 非B</t>
+  </si>
+  <si>
+    <t>👉 用：ものの</t>
+  </si>
+  <si>
+    <t>例：</t>
+  </si>
+  <si>
+    <t>経験はあるものの、結果は出せなかった。</t>
+  </si>
+  <si>
+    <t>② 是“让步承认型”？</t>
+  </si>
+  <si>
+    <t>承认 A</t>
+  </si>
+  <si>
+    <t>但仍然 B</t>
+  </si>
+  <si>
+    <t>👉 用：とはいえ</t>
+  </si>
+  <si>
+    <t>若いとはいえ、責任はある。</t>
+  </si>
+  <si>
+    <t>📌 多见于议论文</t>
+  </si>
+  <si>
+    <t>③ 是“心理矛盾型”？（主语必须一致）</t>
+  </si>
+  <si>
+    <t>明知 A</t>
+  </si>
+  <si>
+    <t>却做 B</t>
+  </si>
+  <si>
+    <t>👉 用：ながら（も）</t>
+  </si>
+  <si>
+    <t>⚠ 主语必须相同</t>
+  </si>
+  <si>
+    <t>④ 是“情绪批评型”？</t>
+  </si>
+  <si>
+    <t>明明 A</t>
+  </si>
+  <si>
+    <t>却（带不满）B</t>
+  </si>
+  <si>
+    <t>👉 用：くせに</t>
+  </si>
+  <si>
+    <t>📌 强主观</t>
+  </si>
+  <si>
+    <t>⑤ 是“客观抗条件型”？</t>
+  </si>
+  <si>
+    <t>尽管 A</t>
+  </si>
+  <si>
+    <t>仍然 B</t>
+  </si>
+  <si>
+    <t>👉 用：にもかかわらず</t>
+  </si>
+  <si>
+    <t>📌 新闻论文常见</t>
+  </si>
+  <si>
+    <t>⑥ 是“程度反转型”？</t>
+  </si>
+  <si>
+    <t>不是 A</t>
+  </si>
+  <si>
+    <t>反而更 B</t>
+  </si>
+  <si>
+    <t>👉 用：どころか</t>
+  </si>
+  <si>
+    <t>📌 常配：</t>
+  </si>
+  <si>
+    <t>むしろ</t>
+  </si>
+  <si>
+    <t>一方だ</t>
+  </si>
+  <si>
+    <t>かえって</t>
+  </si>
+  <si>
+    <t>⑦ 是“正向升级型”？</t>
+  </si>
+  <si>
+    <t>不仅 A</t>
+  </si>
+  <si>
+    <t>而且 B</t>
+  </si>
+  <si>
+    <t>👉 用：ばかりか</t>
+  </si>
+  <si>
+    <t>英語ばかりか、中国語も話せる。</t>
+  </si>
+  <si>
+    <t>🎯 结构分层图（超重要）</t>
+  </si>
+  <si>
+    <t>逆接文法</t>
+  </si>
+  <si>
+    <t>│</t>
+  </si>
+  <si>
+    <t>├── 普通落差 → ものの</t>
+  </si>
+  <si>
+    <t>├── 议论让步 → とはいえ</t>
+  </si>
+  <si>
+    <t>├── 心理冲突（同主语） → ながら</t>
+  </si>
+  <si>
+    <t>├── 情绪批评 → くせに</t>
+  </si>
+  <si>
+    <t>├── 客观正式 → にもかかわらず</t>
+  </si>
+  <si>
+    <t>├── 反向升级 → どころか</t>
+  </si>
+  <si>
+    <t>└── 正向追加 → ばかりか</t>
+  </si>
+  <si>
+    <t>🧠 真正的考试秒杀流程</t>
+  </si>
+  <si>
+    <t>看到题目，按顺序判断：</t>
+  </si>
+  <si>
+    <t>① 有情绪吗？</t>
+  </si>
+  <si>
+    <t>→ 有强烈批评 → くせに</t>
+  </si>
+  <si>
+    <t>② 主语一样吗？心理行为吗？</t>
+  </si>
+  <si>
+    <t>→ 是 → ながら</t>
+  </si>
+  <si>
+    <t>③ 有“むしろ / 一方だ / 反而”吗？</t>
+  </si>
+  <si>
+    <t>④ 是新闻/报告口吻？</t>
+  </si>
+  <si>
+    <t>⑤ 是议论文口吻？</t>
+  </si>
+  <si>
+    <t>⑥ 都不是 → ものの</t>
+  </si>
+  <si>
+    <t>⑦ 是“不仅而且”？</t>
+  </si>
+  <si>
+    <t>A. 看到“ますます / むしろ / 一方だ”</t>
+  </si>
+  <si>
+    <t>→ 100% どころか</t>
+  </si>
+  <si>
+    <t>B. 主语一致 + 心理行为</t>
+  </si>
+  <si>
+    <t>C. 新闻报道口吻</t>
+  </si>
+  <si>
+    <t>D. 议论文语气</t>
+  </si>
+  <si>
+    <t>① 外观感觉（看到样子）</t>
+  </si>
+  <si>
+    <t>用法</t>
+  </si>
+  <si>
+    <t>语气</t>
+  </si>
+  <si>
+    <t>〜そうだ（様態）</t>
+  </si>
+  <si>
+    <t>看起来要…</t>
+  </si>
+  <si>
+    <t>最直观</t>
+  </si>
+  <si>
+    <t>〜ようだ</t>
+  </si>
+  <si>
+    <t>看来…</t>
+  </si>
+  <si>
+    <t>〜みたいだ</t>
+  </si>
+  <si>
+    <t>好像…</t>
+  </si>
+  <si>
+    <t>口语</t>
+  </si>
+  <si>
+    <t>雨が降りそうだ。（马上要下）</t>
+  </si>
+  <si>
+    <t>雨が降るようだ。（看样子会下）</t>
+  </si>
+  <si>
+    <t>雨が降るみたいだ。（好像会下）</t>
+  </si>
+  <si>
+    <t>② 听别人说（传闻）</t>
+  </si>
+  <si>
+    <t>〜そうだ（伝聞）</t>
+  </si>
+  <si>
+    <t>听说</t>
+  </si>
+  <si>
+    <t>〜らしい</t>
+  </si>
+  <si>
+    <t>听说 + 有那种“典型感觉”</t>
+  </si>
+  <si>
+    <t>彼は結婚したそうだ。（听说）</t>
+  </si>
+  <si>
+    <t>彼は結婚したらしい。（听说 + 可信度稍高）</t>
+  </si>
+  <si>
+    <t>③ 根据客观事实推测</t>
+  </si>
+  <si>
+    <t>强度</t>
+  </si>
+  <si>
+    <t>〜はずだ</t>
+  </si>
+  <si>
+    <t>应该（有根据）</t>
+  </si>
+  <si>
+    <t>〜に違いない</t>
+  </si>
+  <si>
+    <t>一定是（确信）</t>
+  </si>
+  <si>
+    <t>看来（逻辑判断）</t>
+  </si>
+  <si>
+    <t>彼は来るはずだ。（约好了）</t>
+  </si>
+  <si>
+    <t>彼は来たに違いない。（确信）</t>
+  </si>
+  <si>
+    <t>彼は来たようだ。（推测）</t>
+  </si>
+  <si>
+    <t>④ 可能性</t>
+  </si>
+  <si>
+    <t>〜かもしれない</t>
+  </si>
+  <si>
+    <t>可能</t>
+  </si>
+  <si>
+    <t>〜おそれがある</t>
+  </si>
+  <si>
+    <t>恐怕（负面）</t>
+  </si>
+  <si>
+    <t>雨が降るかもしれない。</t>
+  </si>
+  <si>
+    <t>事故が起こるおそれがある。</t>
+  </si>
+  <si>
+    <t>二、强度排序（超重要）</t>
+  </si>
+  <si>
+    <t>かもしれない</t>
+  </si>
+  <si>
+    <t>↓</t>
+  </si>
+  <si>
+    <t>らしい</t>
+  </si>
+  <si>
+    <t>ようだ</t>
+  </si>
+  <si>
+    <t>はずだ</t>
+  </si>
+  <si>
+    <t>に違いない</t>
+  </si>
+  <si>
+    <t>🧠 三、最容易混的对比</t>
+  </si>
+  <si>
+    <t>① らしい vs ようだ</t>
+  </si>
+  <si>
+    <t>自己观察推测</t>
+  </si>
+  <si>
+    <t>有“典型性”</t>
+  </si>
+  <si>
+    <t>有逻辑根据</t>
+  </si>
+  <si>
+    <t>彼は医者らしい。（听说是医生 / 有医生那样子）</t>
+  </si>
+  <si>
+    <t>彼は医者のようだ。（根据情况判断）</t>
+  </si>
+  <si>
+    <t>② そうだ（様態） vs そうだ（伝聞）</t>
+  </si>
+  <si>
+    <t>样态</t>
+  </si>
+  <si>
+    <t>传闻</t>
+  </si>
+  <si>
+    <t>动词ます形去ます</t>
+  </si>
+  <si>
+    <t>普通形</t>
+  </si>
+  <si>
+    <t>降りそうだ</t>
+  </si>
+  <si>
+    <t>降るそうだ</t>
+  </si>
+  <si>
+    <t>③ はずだ vs に違いない</t>
+  </si>
+  <si>
+    <t>有客观根据</t>
+  </si>
+  <si>
+    <t>强主观确信</t>
+  </si>
+  <si>
+    <t>比较理性</t>
+  </si>
+  <si>
+    <t>强断定</t>
+  </si>
+  <si>
+    <t>④ ようだ vs みたいだ</t>
+  </si>
+  <si>
+    <t>みたいだ</t>
+  </si>
+  <si>
+    <t>书面</t>
+  </si>
+  <si>
+    <t>正式</t>
+  </si>
+  <si>
+    <t>随便</t>
+  </si>
+  <si>
+    <t>🧠 四、考试秒杀流程</t>
+  </si>
+  <si>
+    <t>看到题目，先问：</t>
+  </si>
+  <si>
+    <t>① 是听别人说的吗？</t>
+  </si>
+  <si>
+    <t>→ そうだ（伝聞） / らしい</t>
+  </si>
+  <si>
+    <t>② 是看到样子判断？</t>
+  </si>
+  <si>
+    <t>→ そうだ（様態）</t>
+  </si>
+  <si>
+    <t>③ 是逻辑推理？</t>
+  </si>
+  <si>
+    <t>→ ようだ</t>
+  </si>
+  <si>
+    <t>④ 是应该发生？</t>
+  </si>
+  <si>
+    <t>→ はずだ</t>
+  </si>
+  <si>
+    <t>⑤ 是非常确信？</t>
+  </si>
+  <si>
+    <t>→ に違いない</t>
+  </si>
+  <si>
+    <t>⑥ 是可能性？</t>
+  </si>
+  <si>
+    <t>→ かもしれない</t>
+  </si>
+  <si>
+    <t>⑦ 是负面风险？</t>
+  </si>
+  <si>
+    <t>→ おそれがある</t>
   </si>
 </sst>
 </file>
@@ -4715,4 +5934,2197 @@
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E6BA163-7E8D-48C3-82FC-DC4252385895}">
+  <dimension ref="B2:E458"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D3" t="s">
+        <v>384</v>
+      </c>
+      <c r="E3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>524</v>
+      </c>
+      <c r="C4" t="s">
+        <v>443</v>
+      </c>
+      <c r="D4" t="s">
+        <v>384</v>
+      </c>
+      <c r="E4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C5" t="s">
+        <v>386</v>
+      </c>
+      <c r="D5" t="s">
+        <v>387</v>
+      </c>
+      <c r="E5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C6" t="s">
+        <v>446</v>
+      </c>
+      <c r="D6" t="s">
+        <v>389</v>
+      </c>
+      <c r="E6" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>390</v>
+      </c>
+      <c r="C7" t="s">
+        <v>448</v>
+      </c>
+      <c r="D7" t="s">
+        <v>384</v>
+      </c>
+      <c r="E7" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>391</v>
+      </c>
+      <c r="C8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D8" t="s">
+        <v>392</v>
+      </c>
+      <c r="E8" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>393</v>
+      </c>
+      <c r="C9" t="s">
+        <v>452</v>
+      </c>
+      <c r="D9" t="s">
+        <v>394</v>
+      </c>
+      <c r="E9" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>395</v>
+      </c>
+      <c r="C10" t="s">
+        <v>454</v>
+      </c>
+      <c r="D10" t="s">
+        <v>396</v>
+      </c>
+      <c r="E10" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>397</v>
+      </c>
+      <c r="C11" t="s">
+        <v>398</v>
+      </c>
+      <c r="D11" t="s">
+        <v>399</v>
+      </c>
+      <c r="E11" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>400</v>
+      </c>
+      <c r="C12" t="s">
+        <v>457</v>
+      </c>
+      <c r="D12" t="s">
+        <v>392</v>
+      </c>
+      <c r="E12" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>401</v>
+      </c>
+      <c r="C13" t="s">
+        <v>459</v>
+      </c>
+      <c r="D13" t="s">
+        <v>402</v>
+      </c>
+      <c r="E13" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>403</v>
+      </c>
+      <c r="C14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D14" t="s">
+        <v>404</v>
+      </c>
+      <c r="E14" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>405</v>
+      </c>
+      <c r="C15" t="s">
+        <v>463</v>
+      </c>
+      <c r="D15" t="s">
+        <v>406</v>
+      </c>
+      <c r="E15" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>407</v>
+      </c>
+      <c r="C16" t="s">
+        <v>465</v>
+      </c>
+      <c r="D16" t="s">
+        <v>406</v>
+      </c>
+      <c r="E16" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>408</v>
+      </c>
+      <c r="C17" t="s">
+        <v>467</v>
+      </c>
+      <c r="D17" t="s">
+        <v>409</v>
+      </c>
+      <c r="E17" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>410</v>
+      </c>
+      <c r="C18" t="s">
+        <v>469</v>
+      </c>
+      <c r="D18" t="s">
+        <v>411</v>
+      </c>
+      <c r="E18" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>412</v>
+      </c>
+      <c r="C19" t="s">
+        <v>413</v>
+      </c>
+      <c r="D19" t="s">
+        <v>471</v>
+      </c>
+      <c r="E19" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>414</v>
+      </c>
+      <c r="C20" t="s">
+        <v>415</v>
+      </c>
+      <c r="D20" t="s">
+        <v>416</v>
+      </c>
+      <c r="E20" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>417</v>
+      </c>
+      <c r="C21" t="s">
+        <v>418</v>
+      </c>
+      <c r="D21" t="s">
+        <v>474</v>
+      </c>
+      <c r="E21" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>419</v>
+      </c>
+      <c r="C22" t="s">
+        <v>420</v>
+      </c>
+      <c r="D22" t="s">
+        <v>476</v>
+      </c>
+      <c r="E22" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>421</v>
+      </c>
+      <c r="C23" t="s">
+        <v>478</v>
+      </c>
+      <c r="D23" t="s">
+        <v>422</v>
+      </c>
+      <c r="E23" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>423</v>
+      </c>
+      <c r="C24" t="s">
+        <v>480</v>
+      </c>
+      <c r="D24" t="s">
+        <v>424</v>
+      </c>
+      <c r="E24" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>425</v>
+      </c>
+      <c r="C25" t="s">
+        <v>482</v>
+      </c>
+      <c r="D25" t="s">
+        <v>426</v>
+      </c>
+      <c r="E25" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>427</v>
+      </c>
+      <c r="C26" t="s">
+        <v>484</v>
+      </c>
+      <c r="D26" t="s">
+        <v>428</v>
+      </c>
+      <c r="E26" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>429</v>
+      </c>
+      <c r="C27" t="s">
+        <v>486</v>
+      </c>
+      <c r="D27" t="s">
+        <v>430</v>
+      </c>
+      <c r="E27" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>431</v>
+      </c>
+      <c r="C28" t="s">
+        <v>488</v>
+      </c>
+      <c r="D28" t="s">
+        <v>432</v>
+      </c>
+      <c r="E28" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>433</v>
+      </c>
+      <c r="C29" t="s">
+        <v>490</v>
+      </c>
+      <c r="D29" t="s">
+        <v>491</v>
+      </c>
+      <c r="E29" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>434</v>
+      </c>
+      <c r="C30" t="s">
+        <v>493</v>
+      </c>
+      <c r="D30" t="s">
+        <v>435</v>
+      </c>
+      <c r="E30" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>436</v>
+      </c>
+      <c r="C31" t="s">
+        <v>437</v>
+      </c>
+      <c r="D31" t="s">
+        <v>438</v>
+      </c>
+      <c r="E31" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>439</v>
+      </c>
+      <c r="C32" t="s">
+        <v>496</v>
+      </c>
+      <c r="D32" t="s">
+        <v>440</v>
+      </c>
+      <c r="E32" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>379</v>
+      </c>
+      <c r="C50" t="s">
+        <v>381</v>
+      </c>
+      <c r="D50" t="s">
+        <v>380</v>
+      </c>
+      <c r="E50" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>382</v>
+      </c>
+      <c r="C51" t="s">
+        <v>384</v>
+      </c>
+      <c r="D51" t="s">
+        <v>513</v>
+      </c>
+      <c r="E51" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>414</v>
+      </c>
+      <c r="C52" t="s">
+        <v>515</v>
+      </c>
+      <c r="D52" t="s">
+        <v>516</v>
+      </c>
+      <c r="E52" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>518</v>
+      </c>
+      <c r="C53" t="s">
+        <v>515</v>
+      </c>
+      <c r="D53" t="s">
+        <v>519</v>
+      </c>
+      <c r="E53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>521</v>
+      </c>
+      <c r="C54" t="s">
+        <v>522</v>
+      </c>
+      <c r="D54" t="s">
+        <v>454</v>
+      </c>
+      <c r="E54" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>379</v>
+      </c>
+      <c r="C59" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>527</v>
+      </c>
+      <c r="C60" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>529</v>
+      </c>
+      <c r="C61" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>531</v>
+      </c>
+      <c r="C62" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>533</v>
+      </c>
+      <c r="C63" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>535</v>
+      </c>
+      <c r="C64" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>537</v>
+      </c>
+      <c r="C65" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>539</v>
+      </c>
+      <c r="C66" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B104" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B134" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B138" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B140" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B142" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B146" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B148" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B150" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B152" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B154" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B156" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B158" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B162" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B164" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B166" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B168" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B170" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B172" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B174" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B176" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B178" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B180" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B184" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B186" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B188" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B190" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B192" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B194" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B196" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B198" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B200" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B201" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B205" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B207" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B209" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B211" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B213" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B215" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B217" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B219" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B221" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B223" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B227" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B229" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B231" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B232" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B233" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B234" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B235" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B236" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="237" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B237" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="241" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B241" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="243" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B243" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="245" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B245" t="s">
+        <v>527</v>
+      </c>
+      <c r="C245" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="246" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B246" t="s">
+        <v>601</v>
+      </c>
+      <c r="C246" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="247" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B247" t="s">
+        <v>603</v>
+      </c>
+      <c r="C247" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="250" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B250" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="252" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B252" t="s">
+        <v>606</v>
+      </c>
+      <c r="C252" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="253" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B253" t="s">
+        <v>607</v>
+      </c>
+      <c r="C253" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="254" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B254" t="s">
+        <v>609</v>
+      </c>
+      <c r="C254" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="257" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B257" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="259" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B259" t="s">
+        <v>537</v>
+      </c>
+      <c r="C259" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="260" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B260" t="s">
+        <v>612</v>
+      </c>
+      <c r="C260" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="261" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B261" t="s">
+        <v>613</v>
+      </c>
+      <c r="C261" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="264" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B264" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="266" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B266" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="268" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B268" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="269" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B269" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="271" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B271" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="272" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B272" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="274" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B274" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="275" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B275" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="277" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B277" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="278" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B278" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="280" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B280" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="281" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B281" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="283" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B283" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="284" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B284" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="286" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B286" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="287" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B287" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="290" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B290" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="292" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B292" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="294" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B294" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="296" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B296" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="297" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B297" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="299" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B299" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="301" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B301" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="302" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B302" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="306" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B306" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="308" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B308" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="309" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B309" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="311" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B311" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="313" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B313" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="314" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B314" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="316" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B316" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="320" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B320" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="322" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B322" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="323" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B323" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="325" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B325" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="327" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B327" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="328" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B328" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="330" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B330" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="334" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B334" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="336" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B336" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="337" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B337" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="339" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B339" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="341" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B341" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="342" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B342" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="344" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B344" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="348" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B348" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="350" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B350" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="351" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B351" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="353" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B353" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="355" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B355" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="356" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B356" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="358" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B358" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="362" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B362" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="364" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B364" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="365" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B365" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="367" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B367" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="369" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B369" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="370" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B370" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="372" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B372" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="374" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B374" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="376" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B376" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="378" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B378" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="382" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B382" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="384" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B384" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="385" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B385" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="387" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B387" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="389" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B389" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="390" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B390" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="394" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B394" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="396" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B396" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="397" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B397" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="398" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B398" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="399" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B399" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="400" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B400" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="401" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B401" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="402" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B402" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="403" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B403" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="404" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B404" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="405" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B405" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="406" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B406" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="407" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B407" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="408" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B408" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="409" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B409" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="410" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B410" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="414" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B414" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="416" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B416" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="418" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B418" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="419" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B419" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="421" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B421" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="422" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B422" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="424" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B424" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="425" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B425" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="427" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B427" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="428" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B428" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="430" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B430" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="431" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B431" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="433" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B433" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="435" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B435" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="436" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B436" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="438" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B438" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="440" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B440" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="444" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B444" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="446" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B446" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="450" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B450" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="452" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B452" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="456" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B456" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="458" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B458" t="s">
+        <v>630</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3BA435-5C99-45F7-B0B1-193B4E7F9193}">
+  <dimension ref="B1:D139"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C3" t="s">
+        <v>700</v>
+      </c>
+      <c r="D3" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>702</v>
+      </c>
+      <c r="C4" t="s">
+        <v>703</v>
+      </c>
+      <c r="D4" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>705</v>
+      </c>
+      <c r="C5" t="s">
+        <v>706</v>
+      </c>
+      <c r="D5" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>707</v>
+      </c>
+      <c r="C6" t="s">
+        <v>708</v>
+      </c>
+      <c r="D6" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>379</v>
+      </c>
+      <c r="C20" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>714</v>
+      </c>
+      <c r="C21" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>716</v>
+      </c>
+      <c r="C22" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>379</v>
+      </c>
+      <c r="C34" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>722</v>
+      </c>
+      <c r="C35" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>724</v>
+      </c>
+      <c r="C36" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>705</v>
+      </c>
+      <c r="C37" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>379</v>
+      </c>
+      <c r="C51" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>731</v>
+      </c>
+      <c r="C52" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>733</v>
+      </c>
+      <c r="C53" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>740</v>
+      </c>
+      <c r="C84" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>715</v>
+      </c>
+      <c r="C85" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>747</v>
+      </c>
+      <c r="C86" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B95" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>752</v>
+      </c>
+      <c r="C97" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
+        <v>754</v>
+      </c>
+      <c r="C98" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>756</v>
+      </c>
+      <c r="C99" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B104" t="s">
+        <v>742</v>
+      </c>
+      <c r="C104" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
+        <v>759</v>
+      </c>
+      <c r="C105" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B106" t="s">
+        <v>761</v>
+      </c>
+      <c r="C106" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B111" t="s">
+        <v>741</v>
+      </c>
+      <c r="C111" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B112" t="s">
+        <v>765</v>
+      </c>
+      <c r="C112" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
+        <v>766</v>
+      </c>
+      <c r="C113" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B116" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B118" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B133" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B135" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B136" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B138" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B139" t="s">
+        <v>783</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>